--- a/.helix/config.xlsx
+++ b/.helix/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saryal/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saryal/Documents/personal/workspace/aem-eds/.helix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEF3378-E137-6947-8396-B6978F1CA85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF02AC2-C7B8-9549-9B2C-0B75F4454BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7000" yWindow="5220" windowWidth="28040" windowHeight="17440" xr2:uid="{BA371A41-EEAF-0D48-A969-E5CC29522C53}"/>
+    <workbookView xWindow="6520" yWindow="4900" windowWidth="28040" windowHeight="17440" xr2:uid="{BA371A41-EEAF-0D48-A969-E5CC29522C53}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -77,6 +77,13 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -101,10 +108,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -448,26 +465,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="b">
+      <c r="B3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
